--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,23 +451,23 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:EndOfEligibility</t>
-  </si>
-  <si>
-    <t>EndOfEligibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-EndOfEligibility}
+    <t>CoverageEligibilityResponse.extension:fristende</t>
+  </si>
+  <si>
+    <t>fristende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fristende}
 </t>
   </si>
   <si>
     <t>"Fristende"</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:VAEStatus</t>
-  </si>
-  <si>
-    <t>VAEStatus</t>
+    <t>CoverageEligibilityResponse.extension:vaeStatus</t>
+  </si>
+  <si>
+    <t>vaeStatus</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vaestatus}
@@ -477,26 +477,26 @@
     <t>"VAEST - Status der Versichertenanspruchserklärung"</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:MealCostExcemption</t>
-  </si>
-  <si>
-    <t>MealCostExcemption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-MealCostExcemption}
+    <t>CoverageEligibilityResponse.extension:verpflegskostenBeitragsbefreiung</t>
+  </si>
+  <si>
+    <t>verpflegskostenBeitragsbefreiung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verpflegskostenBeitragsbefreiung}
 </t>
   </si>
   <si>
     <t>"VKBEFR – Verpflegskosten-Beitragsbefreiung"</t>
   </si>
   <si>
-    <t>CoverageEligibilityResponse.extension:NumberOfPreviouslyPaidDays</t>
-  </si>
-  <si>
-    <t>NumberOfPreviouslyPaidDays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-NumberOfPreviouslyPaidDays}
+    <t>CoverageEligibilityResponse.extension:vortageanzahlAufKostenbeitrag</t>
+  </si>
+  <si>
+    <t>vortageanzahlAufKostenbeitrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-vortageanzahlAufKostenbeitrag}
 </t>
   </si>
   <si>
@@ -1635,9 +1635,9 @@
   <dimension ref="A1:AN70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.5703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="68.3359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="65.5703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="32.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1645,7 +1645,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="90.52734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$70</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1464,6 +1467,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1803,7 +1821,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1915,7 +1933,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2029,7 +2047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2141,7 +2159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -2255,7 +2273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -2369,7 +2387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2483,7 +2501,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2597,7 +2615,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -2707,7 +2725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -2728,7 +2746,7 @@
         <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2821,7 +2839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2842,7 +2860,7 @@
         <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -2935,7 +2953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
@@ -3049,7 +3067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>153</v>
       </c>
@@ -3163,7 +3181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>157</v>
       </c>
@@ -3279,7 +3297,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>164</v>
       </c>
@@ -3393,7 +3411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>171</v>
       </c>
@@ -3509,7 +3527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>180</v>
       </c>
@@ -3623,7 +3641,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>187</v>
       </c>
@@ -3737,7 +3755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>195</v>
       </c>
@@ -3849,7 +3867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>199</v>
       </c>
@@ -3961,7 +3979,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>206</v>
       </c>
@@ -4075,7 +4093,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>210</v>
       </c>
@@ -4191,7 +4209,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>215</v>
       </c>
@@ -4301,7 +4319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>221</v>
       </c>
@@ -4413,7 +4431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>225</v>
       </c>
@@ -4527,7 +4545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>232</v>
       </c>
@@ -4641,7 +4659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>238</v>
       </c>
@@ -4755,7 +4773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>245</v>
       </c>
@@ -4869,7 +4887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>253</v>
       </c>
@@ -4985,7 +5003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>260</v>
       </c>
@@ -5099,7 +5117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>265</v>
       </c>
@@ -5213,7 +5231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>270</v>
       </c>
@@ -5329,7 +5347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>275</v>
       </c>
@@ -5441,7 +5459,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>276</v>
       </c>
@@ -5555,7 +5573,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>277</v>
       </c>
@@ -5671,7 +5689,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>278</v>
       </c>
@@ -5785,7 +5803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>283</v>
       </c>
@@ -5899,7 +5917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>288</v>
       </c>
@@ -6013,7 +6031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>293</v>
       </c>
@@ -6125,7 +6143,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>297</v>
       </c>
@@ -6237,7 +6255,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>298</v>
       </c>
@@ -6351,7 +6369,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>299</v>
       </c>
@@ -6467,7 +6485,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>300</v>
       </c>
@@ -6583,7 +6601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>308</v>
       </c>
@@ -6699,7 +6717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>316</v>
       </c>
@@ -6815,7 +6833,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>323</v>
       </c>
@@ -6929,7 +6947,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>328</v>
       </c>
@@ -7043,7 +7061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>332</v>
       </c>
@@ -7159,7 +7177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>337</v>
       </c>
@@ -7275,7 +7293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>342</v>
       </c>
@@ -7389,7 +7407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>348</v>
       </c>
@@ -7503,7 +7521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>354</v>
       </c>
@@ -7617,7 +7635,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>359</v>
       </c>
@@ -7729,7 +7747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>362</v>
       </c>
@@ -7841,7 +7859,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>363</v>
       </c>
@@ -7955,7 +7973,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>364</v>
       </c>
@@ -8071,7 +8089,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>365</v>
       </c>
@@ -8187,7 +8205,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>371</v>
       </c>
@@ -8301,7 +8319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>376</v>
       </c>
@@ -8415,7 +8433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>380</v>
       </c>
@@ -8529,7 +8547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>384</v>
       </c>
@@ -8643,7 +8661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>390</v>
       </c>
@@ -8757,7 +8775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>394</v>
       </c>
@@ -8871,7 +8889,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>400</v>
       </c>
@@ -8987,7 +9005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>408</v>
       </c>
@@ -9101,7 +9119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>412</v>
       </c>
@@ -9213,7 +9231,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>413</v>
       </c>
@@ -9327,7 +9345,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>414</v>
       </c>
@@ -9443,7 +9461,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>415</v>
       </c>
@@ -9557,7 +9575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>421</v>
       </c>
@@ -9674,6 +9692,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN70">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI69">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverageEligibilityResponse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
